--- a/dataset/construct/dataset_splits/data_size/5_percent/tum/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/tum/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2583</v>
+        <v>922</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,82 +625,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.0467322926965</v>
+        <v>75.0324815258448</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>26.4721074380165</v>
       </c>
       <c r="E2" t="n">
-        <v>26.2975778546712</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="I2" t="n">
-        <v>1320</v>
+        <v>391</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>977</v>
       </c>
       <c r="L2" t="n">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="N2" t="n">
-        <v>1383</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>26.5</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>27.3745861981156</v>
       </c>
       <c r="X2" t="n">
-        <v>24.65</v>
+        <v>26.7218716216114</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.220216606498195</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.3439993862133</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -724,39 +709,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>154</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2257</v>
+        <v>452</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,77 +738,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.1240494207418</v>
+        <v>75.6426521345096</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>31.4359113034072</v>
       </c>
       <c r="E3" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>679</v>
+      </c>
+      <c r="I3" t="n">
+        <v>324</v>
+      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>338.1</v>
+        <v>1087</v>
       </c>
       <c r="L3" t="n">
-        <v>245.5</v>
+        <v>18.7</v>
       </c>
       <c r="M3" t="n">
-        <v>290.6</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
-        <v>874.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>61.6</v>
+        <v>45.7</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.0641711229947</v>
       </c>
       <c r="X3" t="n">
-        <v>27.65</v>
+        <v>23.2857506244092</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.16887417218543</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.2154316271963</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.9211850934372</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -861,19 +837,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
